--- a/food_beverage_order_forms/039_identify_your_culinary_style--food_beverage_order_forms.xlsx
+++ b/food_beverage_order_forms/039_identify_your_culinary_style--food_beverage_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1060,8 +1060,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'italian'}</t>
+          <t>italian</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'Italian'}</t>
+          <t>Italian</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'mexican'}</t>
+          <t>mexican</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'Mexican'}</t>
+          <t>Mexican</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'chinese'}</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'Chinese'}</t>
+          <t>Chinese</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'japanese'}</t>
+          <t>japanese</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'Japanese'}</t>
+          <t>Japanese</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'indian'}</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'Indian'}</t>
+          <t>Indian</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'korean'}</t>
+          <t>korean</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'Korean'}</t>
+          <t>Korean</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'grilling'}</t>
+          <t>grilling</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'Grilling'}</t>
+          <t>Grilling</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'baking'}</t>
+          <t>baking</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'Baking'}</t>
+          <t>Baking</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'boiling'}</t>
+          <t>boiling</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'Boiling'}</t>
+          <t>Boiling</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'steaming'}</t>
+          <t>steaming</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'Steaming'}</t>
+          <t>Steaming</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'frying'}</t>
+          <t>frying</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'Frying'}</t>
+          <t>Frying</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'roasting'}</t>
+          <t>roasting</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'Roasting'}</t>
+          <t>Roasting</t>
         </is>
       </c>
     </row>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'name':_'meat-based'}</t>
+          <t>meat-based</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'name': 'Meat-based'}</t>
+          <t>Meat-based</t>
         </is>
       </c>
     </row>
@@ -1327,12 +1327,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'name':_'seafood-based'}</t>
+          <t>seafood-based</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'name': 'Seafood-based'}</t>
+          <t>Seafood-based</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'name':_'dairy-based'}</t>
+          <t>dairy-based</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'name': 'Dairy-based'}</t>
+          <t>Dairy-based</t>
         </is>
       </c>
     </row>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'name':_'vegan-based'}</t>
+          <t>vegan-based</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'name': 'Vegan-based'}</t>
+          <t>Vegan-based</t>
         </is>
       </c>
     </row>
@@ -1378,12 +1378,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'name':_'gluten-free'}</t>
+          <t>gluten-free</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'name': 'Gluten-free'}</t>
+          <t>Gluten-free</t>
         </is>
       </c>
     </row>
@@ -1395,12 +1395,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'name':_'low-sodium'}</t>
+          <t>low-sodium</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'name': 'Low-Sodium'}</t>
+          <t>Low-Sodium</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'name':_'low-fat'}</t>
+          <t>low-fat</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'name': 'Low-Fat'}</t>
+          <t>Low-Fat</t>
         </is>
       </c>
     </row>
@@ -1429,12 +1429,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'name':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'name': 'Morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'name':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'name': 'Afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1463,12 +1463,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'name':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'name': 'Evening'}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -1480,12 +1480,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'name':_'all-day'}</t>
+          <t>all-day</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'name': 'All-day'}</t>
+          <t>All-day</t>
         </is>
       </c>
     </row>
@@ -1497,12 +1497,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'name':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'name': 'Yes'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1514,12 +1514,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'name':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'name': 'No'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'name':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'name': 'Unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
@@ -1548,12 +1548,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'name':_'grains'}</t>
+          <t>grains</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'name': 'Grains'}</t>
+          <t>Grains</t>
         </is>
       </c>
     </row>
@@ -1565,12 +1565,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'name':_'fruits'}</t>
+          <t>fruits</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'name': 'Fruits'}</t>
+          <t>Fruits</t>
         </is>
       </c>
     </row>
@@ -1582,12 +1582,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'name':_'vegetables'}</t>
+          <t>vegetables</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'name': 'Vegetables'}</t>
+          <t>Vegetables</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'name':_'nuts'}</t>
+          <t>nuts</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'name': 'Nuts'}</t>
+          <t>Nuts</t>
         </is>
       </c>
     </row>
@@ -1616,12 +1616,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'name':_'seeds'}</t>
+          <t>seeds</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'name': 'Seeds'}</t>
+          <t>Seeds</t>
         </is>
       </c>
     </row>
@@ -1633,12 +1633,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'name':_'spices'}</t>
+          <t>spices</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'name': 'Spices'}</t>
+          <t>Spices</t>
         </is>
       </c>
     </row>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'name':_'rare'}</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'name': 'Rare'}</t>
+          <t>Rare</t>
         </is>
       </c>
     </row>
@@ -1667,12 +1667,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1684,12 +1684,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'name':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'name': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'name':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'name': 'Morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1718,12 +1718,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'name':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'name': 'Afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1735,12 +1735,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'name':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'name': 'Evening'}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'name':_'all-day'}</t>
+          <t>all-day</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'name': 'All-day'}</t>
+          <t>All-day</t>
         </is>
       </c>
     </row>
@@ -1769,12 +1769,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'name':_'grilled'}</t>
+          <t>grilled</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'name': 'Grilled'}</t>
+          <t>Grilled</t>
         </is>
       </c>
     </row>
@@ -1786,12 +1786,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'name':_'baked'}</t>
+          <t>baked</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'name': 'Baked'}</t>
+          <t>Baked</t>
         </is>
       </c>
     </row>
@@ -1803,12 +1803,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'name':_'steamed'}</t>
+          <t>steamed</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'name': 'Steamed'}</t>
+          <t>Steamed</t>
         </is>
       </c>
     </row>
@@ -1820,12 +1820,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'name':_'roasted'}</t>
+          <t>roasted</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'name': 'Roasted'}</t>
+          <t>Roasted</t>
         </is>
       </c>
     </row>
@@ -1837,12 +1837,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'name':_'breakfast'}</t>
+          <t>breakfast</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'name': 'Breakfast'}</t>
+          <t>Breakfast</t>
         </is>
       </c>
     </row>
@@ -1854,12 +1854,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'name':_'lunch'}</t>
+          <t>lunch</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'name': 'Lunch'}</t>
+          <t>Lunch</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'name':_'dinner'}</t>
+          <t>dinner</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'name': 'Dinner'}</t>
+          <t>Dinner</t>
         </is>
       </c>
     </row>
@@ -1888,12 +1888,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'name':_'snack'}</t>
+          <t>snack</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'name': 'Snack'}</t>
+          <t>Snack</t>
         </is>
       </c>
     </row>
